--- a/data/sample/示例数据/附件6：问题汇总.xlsx
+++ b/data/sample/示例数据/附件6：问题汇总.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$95</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="170">
   <si>
     <t>编号</t>
   </si>
@@ -47,7 +47,7 @@
     <t>多意图</t>
   </si>
   <si>
-    <t>[{"Q": "2024年利润最高的top10企业是哪些？这些企业的利润、销售额年同比是多少？年同比上涨幅度最大的是哪家企业？"}]</t>
+    <t>[{"Q":"2024年利润最高的top10企业是哪些？这些企业的利润、销售额年同比是多少？年同比上涨幅度最大的是哪家企业？"}]</t>
   </si>
   <si>
     <t>B2002</t>
@@ -56,7 +56,7 @@
     <t>意图模糊</t>
   </si>
   <si>
-    <t>[{"Q": "国家医保目录新增的中药产品有哪些"}]</t>
+    <t>[{"Q":"国家医保目录新增的中药产品有哪些"}]</t>
   </si>
   <si>
     <t>B2003</t>
@@ -65,7 +65,481 @@
     <t>归因分析</t>
   </si>
   <si>
-    <t>[{"Q": "华润三九近三年的主营业务收入情况做可视化绘图"}, {"Q": "主营业务收入上升的原因是什么"}]</t>
+    <t>[{"Q":"华润三九近三年的主营业务收入情况做可视化绘图"},{"Q":"主营业务收入上升的原因是什么"}]</t>
+  </si>
+  <si>
+    <t>B2004</t>
+  </si>
+  <si>
+    <t>开放性问题</t>
+  </si>
+  <si>
+    <t>[{"Q":"北向资金占A股每天成交金额的15%，影响力不可谓不大，外资集体撤退大A股还顶得住吗？"}]</t>
+  </si>
+  <si>
+    <t>B2005</t>
+  </si>
+  <si>
+    <t>[{"Q":"片仔癀利润总额是多少"},{"Q":"2025年第三季度的"},{"Q":"同比增长还是下降了？为什么"}]</t>
+  </si>
+  <si>
+    <t>B2006</t>
+  </si>
+  <si>
+    <t>[{"Q":"片仔癀近几年的利润总额变化趋势是什么样的"},{"Q":"涨跌的原因是什么"}]</t>
+  </si>
+  <si>
+    <t>B2007</t>
+  </si>
+  <si>
+    <t>[{"Q":"999与白云山相比，去年收益率最高的是"},{"Q":"分析两家企业收益率差异的原因"},{"Q":"这些数据的来源可靠吗"}]</t>
+  </si>
+  <si>
+    <t>B2008</t>
+  </si>
+  <si>
+    <t>[{"Q":"2025年前三季度，公司实现收入超过200亿元的企业有哪些"},{"Q":"他们有什么共同点？"}]</t>
+  </si>
+  <si>
+    <t>B2009</t>
+  </si>
+  <si>
+    <t>[{"Q":"企业名称：三金，第三季度公司主营业务收入是多少"},{"Q":"2025年第三季度的"},{"Q":"同比涨跌情况及原因分析"}]</t>
+  </si>
+  <si>
+    <t>B2010</t>
+  </si>
+  <si>
+    <t>[{"Q":"分析一下佐力药业2025收入情况，看看有什么变化。"},{"Q":"绘制近3年的收入趋势图"},{"Q":"绘制水平柱状图"},{"Q":"分析收入趋势涨跌原因"}]</t>
+  </si>
+  <si>
+    <t>B2011</t>
+  </si>
+  <si>
+    <t>[{"Q":"哪些企业是亏钱的？"},{"Q":"“亏钱”在业务场景中，指的是经审计财务报表的核心利润指标为负的数据。"},{"Q":"哪些共同因素导致企业亏钱"}]</t>
+  </si>
+  <si>
+    <t>B2012</t>
+  </si>
+  <si>
+    <t>[{"Q":"太极集团2024年研发费用是多少"},{"Q":"销售费用是多少"},{"Q":"上面两个指标与销售收入占比是多少，对销售收入涨跌有什么影响"}]</t>
+  </si>
+  <si>
+    <t>B2013</t>
+  </si>
+  <si>
+    <t>[{"Q":"25年各中药企业研发情况。"}]</t>
+  </si>
+  <si>
+    <t>B2014</t>
+  </si>
+  <si>
+    <t>[{"Q":"对比一下各个中药相关上市企业上半年的销售额，看看谁的增速更快？"},{"Q":"给出的数据是从哪里来的？"}]</t>
+  </si>
+  <si>
+    <t>B2015</t>
+  </si>
+  <si>
+    <t>归因分析；多意图</t>
+  </si>
+  <si>
+    <t>[{"Q":"2025第三季度方盛制药营收多少？同比增长了多少？收入变化的原因是什么"}]</t>
+  </si>
+  <si>
+    <t>B2016</t>
+  </si>
+  <si>
+    <t>融合查询</t>
+  </si>
+  <si>
+    <t>[{"Q":"结合“中药创新药审批提速”政策，查询2025年第三季度研发费用占比前五的中药公司，并提取研报中对这些公司研发管线的评价"}]</t>
+  </si>
+  <si>
+    <t>B2017</t>
+  </si>
+  <si>
+    <t>[{"Q":"从个股研报中筛选出被评为“强烈推荐”的中药公司，统计它们2025年第三季度的平均净利润同比增长率，并与行业均值对比。"}]</t>
+  </si>
+  <si>
+    <t>B2018</t>
+  </si>
+  <si>
+    <t>[{"Q":"《公司信息更新报告：2025H1利润增长亮眼，创新管线布局带来成长空间》提到“随原材料成本下降等带来的利润改善”，请查询以岭药业2024-2025年第三季度的销售毛利率变化，并结合研报解释原因。"}]</t>
+  </si>
+  <si>
+    <t>B2019</t>
+  </si>
+  <si>
+    <t>[{"Q":"《2025年中国中药市场行业研究报告》行业研报指出“当前中药配方颗粒市场规模已达638.4亿元”，请列出2025年第三季度配方颗粒业务收入占比超过30%的公司及其营业总收入同比增长率。"}]</t>
+  </si>
+  <si>
+    <t>B2020</t>
+  </si>
+  <si>
+    <t>[{"Q":"检索2025年研报中提及“海外市场拓展”的中药公司，查询这些公司2025年第三季度的经营性现金流量净额，并对比其国内业务为主的同行水平。"}]</t>
+  </si>
+  <si>
+    <t>B2021</t>
+  </si>
+  <si>
+    <t>[{"Q":"结合个股研报，找出2025年存在“商誉减值风险”的公司，查询其2025年第三季度的资产负债率和净利润情况。"}]</t>
+  </si>
+  <si>
+    <t>B2022</t>
+  </si>
+  <si>
+    <t>[{"Q":"针对2025年下半年流感活动上升，请统计2025年第三季度净利润同比上升的公司数量，并提取研报中对流感对净利润的分析。"}]</t>
+  </si>
+  <si>
+    <t>B2023</t>
+  </si>
+  <si>
+    <t>[{"Q":"检索研报中独家品种纳入医保目录的公司，查询这些公司2025年第三季度的营业总收入增长率，并与未纳入医保的公司对比。"}]</t>
+  </si>
+  <si>
+    <t>B2024</t>
+  </si>
+  <si>
+    <t>[{"Q":"结合2025年个股研报的风险提示，查询存在“应收账款回收风险”的公司2025年第三季度应收账款占营业总收入的比例。"}]</t>
+  </si>
+  <si>
+    <t>B2025</t>
+  </si>
+  <si>
+    <t>[{"Q":"行业研报预测“2025年中药饮片需求增长”，请列出2025年第三季度饮片业务收入排名前十的公司，并提取研报对其市场份额的评价。"}]</t>
+  </si>
+  <si>
+    <t>B2026</t>
+  </si>
+  <si>
+    <t>[{"Q":"检索2025年研报中提到人工智能产业升级相关布局的公司，查询这些公司2025年第三季度的销售费用率变化情况"}]</t>
+  </si>
+  <si>
+    <t>B2027</t>
+  </si>
+  <si>
+    <t>[{"Q":"结合个股研报，找出2025年拟进行“资产重组”的公司，查询其2025年第三季度的总资产和股东权益总额。"},{"Q":"列举的公司名单你确定是对的吗，判断依据是什么？"}]</t>
+  </si>
+  <si>
+    <t>B2028</t>
+  </si>
+  <si>
+    <t>[{"Q":"国家关注养老问题，请查询2025年第三季度老年病相关药品收入占比前五的公司及其净资产收益率。"}]</t>
+  </si>
+  <si>
+    <t>B2029</t>
+  </si>
+  <si>
+    <t>[{"Q":"检索研报中“获得FDA认证”的中药公司，查询其2025年第三季度的海外业务收入及同比增长率。"}]</t>
+  </si>
+  <si>
+    <t>B2030</t>
+  </si>
+  <si>
+    <t>[{"Q":"结合2025年政策研报中“中药集采扩围”的内容，查询集采中标企业2025年第三季度的净利润率变化，并提取研报对集采影响的观点。"}]</t>
+  </si>
+  <si>
+    <t>B2031</t>
+  </si>
+  <si>
+    <t>[{"Q":"找出研报中提及“库存积压”的公司，查询其2025年第三季度的存货周转率，并与行业平均水平对比。"}]</t>
+  </si>
+  <si>
+    <t>B2032</t>
+  </si>
+  <si>
+    <t>[{"Q":"2025年中药电商渠道销售额增长，请查询2025年第三季度销售费用中电商推广费占比前五的公司。"}]</t>
+  </si>
+  <si>
+    <t>B2033</t>
+  </si>
+  <si>
+    <t>[{"Q":"检索2025年个股研报中的“业绩预告”，对比预告净利润与2025年第三季度实际净利润的差异，列出差异率最大的公司。"}]</t>
+  </si>
+  <si>
+    <t>B2034</t>
+  </si>
+  <si>
+    <t>[{"Q":"查询2025年第三季度出口业务占比超过10%的中药公司及其资产负债率。"},{"Q":"你从哪里查询到的数据"}]</t>
+  </si>
+  <si>
+    <t>B2035</t>
+  </si>
+  <si>
+    <t>[{"Q":"找出研报中被评为“行业龙头”的五家公司，查询它们2022-2025年第三季度的营业总收入复合增长率，并提取研报对其龙头地位的分析依据。"}]</t>
+  </si>
+  <si>
+    <t>B2036</t>
+  </si>
+  <si>
+    <t>数据校验</t>
+  </si>
+  <si>
+    <t>[{"Q":"计算2025年第三季度66家公司的资产负债率行业均值"},{"Q":"计算结果是否符合“负债总额/资产总额”"}]</t>
+  </si>
+  <si>
+    <t>B2037</t>
+  </si>
+  <si>
+    <t>[{"Q":"查询云南白药（000538）2025年第三季度的营业总收入"},{"Q":"核心业绩指标表与利润表中的该数值是否一致"}]</t>
+  </si>
+  <si>
+    <t>B2038</t>
+  </si>
+  <si>
+    <t>[{"Q":"统计2025年第三季度净利润同比增长率超过100%的公司"},{"Q":"这些公司的2024年同期净利润是否为正数，若存在基数为负的情况请标注并重新计算增长率。"}]</t>
+  </si>
+  <si>
+    <t>B2039</t>
+  </si>
+  <si>
+    <t>[{"Q":"查询2025年第三季度满足“营收超10亿、负债率低于40%、现金流为正”的公司"},{"Q":"这些公司名单你确定是对的吗"}]</t>
+  </si>
+  <si>
+    <t>B2040</t>
+  </si>
+  <si>
+    <t>[{"Q":"请完成以下分析：①找出2025年第三季度营业总收入前五的中药公司；②计算它们2025年第三季度的资产负债率和销售毛利率；③对比这五家公司的上述指标与行业均值的差异；④提取研报中对这五家公司的核心竞争力评价。"}]</t>
+  </si>
+  <si>
+    <t>B2041</t>
+  </si>
+  <si>
+    <t>[{"Q":"针对云南白药：①查询2022-2025年第三季度的净利润和扣非净利润；②计算各报告期的扣非净利润占比；③分析该占比的变化趋势；④结合研报说明趋势变化的原因。"}]</t>
+  </si>
+  <si>
+    <t>B2042</t>
+  </si>
+  <si>
+    <t>[{"Q":"统计2025年第三季度净利润同比增长的公司数量；计算这些公司的平均研发费用占比；找出其中研发费用占比高于平均水平的公司；生成这些公司的研发费用占比与净利润增长率的散点图"}]</t>
+  </si>
+  <si>
+    <t>B2043</t>
+  </si>
+  <si>
+    <t>[{"Q":"围绕“中药公司短期偿债能力”：①计算2025年第三季度所有公司的流动比率（流动资产/流动负债）；②找出流动比率低于1的公司；③查询这些公司的短期借款金额和货币资金金额；④结合研报分析它们的偿债风险"}]</t>
+  </si>
+  <si>
+    <t>B2044</t>
+  </si>
+  <si>
+    <t>[{"Q":"列出2025年第三季度经营性现金流量净额前十的公司；查询它们2025年第三季度的净利润；计算现金流与净利润的比值；分析比值大于1的公司的现金流质量优势"}]</t>
+  </si>
+  <si>
+    <t>B2045</t>
+  </si>
+  <si>
+    <t>[{"Q":"统计2025年第三季度资产负债率在30%-50%之间的公司数量；计算这些公司的平均净资产收益率；对比该均值与资产负债率高于50%公司的均值差异；结合研报说明资产负债率与净资产收益率的关系"}]</t>
+  </si>
+  <si>
+    <t>B2046</t>
+  </si>
+  <si>
+    <t>[{"Q":"围绕“研发投入与业绩”：①找出2025年第三季度研发费用占比前十的公司；②查询它们2024-2025年第三季度的净利润同比增长率；③对比研发费用占比前十与后十公司的增长率差异；④生成研发费用占比与净利润增长率的对比柱状图。"}]</t>
+  </si>
+  <si>
+    <t>B2047</t>
+  </si>
+  <si>
+    <t>[{"Q":"查询2025年第三季度存货金额前五的公司；计算它们的存货周转率；找出存货周转率低于行业均值的公司；结合研报分析这些公司的存货管理问题"}]</t>
+  </si>
+  <si>
+    <t>B2048</t>
+  </si>
+  <si>
+    <t>[{"Q":"找出2025年第三季度净利润为负的公司；查询它们的资产负债率和经营性现金流量净额；筛选出负债率高于60%且现金流为负的公司；结合研报给出这些公司的风险预警。"}]</t>
+  </si>
+  <si>
+    <t>B2049</t>
+  </si>
+  <si>
+    <t>[{"Q":"围绕“销售费用管控”：①计算2025年第三季度各公司的销售费用率；②找出销售费用率低于行业均值的公司；③查询这些公司的营业总收入和净利润；④分析销售费用管控对净利润的影响。"}]</t>
+  </si>
+  <si>
+    <t>B2050</t>
+  </si>
+  <si>
+    <t>[{"Q":"查询2025年第三季度投资性现金流量净额为负的公司；统计这些公司的数量及占比；找出其中投资现金流净额绝对值最大的三家公司；提取研报中对它们投资项目的说明。"}]</t>
+  </si>
+  <si>
+    <t>B2051</t>
+  </si>
+  <si>
+    <t>[{"Q":"针对2025年第三季度：①计算各公司的净利润率（净利润/营业总收入）；②按净利润率分为“高（&gt;15%）、中（5%-15%）、低（&lt;5%）”三组；③统计每组的公司数量；④对比三组的平均资产负债率差异。"},{"Q":"列举数据来源，并检查数据来源是否可靠，给出可靠性结论"}]</t>
+  </si>
+  <si>
+    <t>B2052</t>
+  </si>
+  <si>
+    <t>[{"Q":"找出2025年第三季度扣非净利润同比增长率超过50%的公司；查询它们的研发费用和销售费用变化情况；分析费用变化对扣非净利润增长的贡献；结合研报预测这些公司的后续业绩。"}]</t>
+  </si>
+  <si>
+    <t>B2053</t>
+  </si>
+  <si>
+    <t>[{"Q":"围绕“现金流与利润匹配度”：①计算2025年第三季度各公司的经营性现金流净额/净利润比值；②找出比值在0.8-1.2之间的公司；③统计这些公司的数量；④对比这些公司与比值偏离区间公司的资产质量。"}]</t>
+  </si>
+  <si>
+    <t>B2054</t>
+  </si>
+  <si>
+    <t>[{"Q":"查询2025年第三季度货币资金占总资产比例前五的公司；②计算它们的投资性现金流量净额；③分析货币资金充裕度与投资支出的关系；④结合研报说明这些公司的资金使用规划。"}]</t>
+  </si>
+  <si>
+    <t>B2055</t>
+  </si>
+  <si>
+    <t>[{"Q":"针对2022-2025年第三季度：①找出连续四个报告期营业总收入增长的公司；②计算这些公司的平均复合增长率；③查询它们的研发投入累计金额；④验证持续增长与研发投入的关联性。"}]</t>
+  </si>
+  <si>
+    <t>B2056</t>
+  </si>
+  <si>
+    <t>[{"Q":"统计2025年第三季度各公司的营业总成本构成（营业成本、销售费用、管理费用、研发费用占比）；②找出营业成本占比最低的公司；③查询该公司的主营业务类型；④结合研报分析其成本控制优势。"}]</t>
+  </si>
+  <si>
+    <t>B2057</t>
+  </si>
+  <si>
+    <t>[{"Q":"围绕“分红潜力”：①计算2025年第三季度各公司的未分配利润/净利润比值；②找出比值高于5的公司；③查询这些公司的资产负债率；④结合研报评估它们的分红可能性。"}]</t>
+  </si>
+  <si>
+    <t>B2058</t>
+  </si>
+  <si>
+    <t>[{"Q":"针对行业龙头公司，查询2022-2025年第三季度的营业总收入"}]</t>
+  </si>
+  <si>
+    <t>B2059</t>
+  </si>
+  <si>
+    <t>[{"Q":"针对三九、白云山、云南白药、片仔癀等企业，查询2022-2025年第三季度的营业总收入；计算各年度的同比增长率；生成营收增长趋势折线图；对比上述公司与行业整体的增长差异。"},{"Q":"数据来源是否可靠？"}]</t>
+  </si>
+  <si>
+    <t>B2060</t>
+  </si>
+  <si>
+    <t>[{"Q":"2025年第三季度香雪制药净利润同比下降50%，请结合财务数据（如营业成本、销售费用变化）和个股研报，分析净利润下降的核心原因"}]</t>
+  </si>
+  <si>
+    <t>B2061</t>
+  </si>
+  <si>
+    <t>[{"Q":"康芝药业2025年第三季度经营性现金流量净额为正，但净利润为负，请结合现金流量表和利润表项目，以及研报信息，解释这种背离现象的原因。"}]</t>
+  </si>
+  <si>
+    <t>B2062</t>
+  </si>
+  <si>
+    <t>[{"Q":"2025年第三季度奇正藏药资产负债率从2024年同期的40%降低至27%，请结合资产负债表项目变化和行业研报（如政策、融资环境），分析负债率下降的原因"}]</t>
+  </si>
+  <si>
+    <t>B2063</t>
+  </si>
+  <si>
+    <t>[{"Q":"达仁堂2025年第三季度销售毛利率同比提升10个百分点，请结合利润表（营业收入、营业成本）和研报（如产品提价、原材料降价），分析毛利率提升的驱动因素。"}]</t>
+  </si>
+  <si>
+    <t>B2064</t>
+  </si>
+  <si>
+    <t>[{"Q":"2025年第三季度康美药业应收账款占营业总收入比例超过50%，请结合资产负债表和研报（如销售模式、客户结构），分析应收账款高企的原因及潜在风险。"}]</t>
+  </si>
+  <si>
+    <t>B2065</t>
+  </si>
+  <si>
+    <t>[{"Q":"佐力药业2025年第三季度研发费用占比同比提升5个百分点，请结合核心业绩指标表和个股研报（如研发管线、政策激励），分析研发投入增加的原因。"}]</t>
+  </si>
+  <si>
+    <t>B2066</t>
+  </si>
+  <si>
+    <t>[{"Q":"2025年第三季度片仔癀存货周转率同比下降30%，请结合资产负债表和行业研报（如市场需求、库存策略），分析存货周转变慢的原因。"}]</t>
+  </si>
+  <si>
+    <t>B2067</t>
+  </si>
+  <si>
+    <t>[{"Q":"东阿阿胶2022-2025年第三季度营业总收入复合增长率达20%，远超行业均值，请结合财务数据和研报（如新品上市、市场拓展），分析高速增长的核心驱动力。"},{"Q":"你确定你给出的分析结论是对的吗"}]</t>
+  </si>
+  <si>
+    <t>B2068</t>
+  </si>
+  <si>
+    <t>[{"Q":"2025年第三季度片仔癀扣非净利润与净利润差值超过1亿元，请结合核心业绩指标表和研报（如资产处置、政府补贴），分析差值较大的原因。"}]</t>
+  </si>
+  <si>
+    <t>B2069</t>
+  </si>
+  <si>
+    <t>[{"Q":"佐力药业2025年第三季度投资性现金流量净额为正且金额较大，请结合现金流量表和个股研报（如处置子公司、理财产品到期），分析投资现金流为正的原因。"}]</t>
+  </si>
+  <si>
+    <t>B2070</t>
+  </si>
+  <si>
+    <t>[{"Q":"2025年第三季度陇神戎发销售费用率同比提升8个百分点，但营业总收入同比下降10%，请结合利润表和研报（如营销活动、市场竞争），分析销售费用率提升的原因。"}]</t>
+  </si>
+  <si>
+    <t>B2071</t>
+  </si>
+  <si>
+    <t>[{"Q":"片仔癀2025年第三季度净资产收益率同比下降5个百分点，请结合资产负债表和利润表，以及行业研报（如利率变化、行业竞争），分析收益率下降的原因。"}]</t>
+  </si>
+  <si>
+    <t>B2072</t>
+  </si>
+  <si>
+    <t>[{"Q":"2025年第三季度新天药业货币资金占总资产比例超过30%，但投资性现金流量净额为负，请结合资产负债表和研报（如战略投资、项目布局），分析资金配置的原因"}]</t>
+  </si>
+  <si>
+    <t>B2073</t>
+  </si>
+  <si>
+    <t>[{"Q":"健民集团2025年第三季度营业总成本同比增长20%，但营业总收入仅增长5%，请结合利润表项目和研报（如原材料涨价、人力成本上升），分析成本增长快于营收的原因。"},{"Q":"你凭什么觉得是这个原因导致了这个问题"}]</t>
+  </si>
+  <si>
+    <t>B2074</t>
+  </si>
+  <si>
+    <t>[{"Q":"2025年第三季度广誉远未分配利润为负数，但净利润为正数，请结合资产负债表和利润表，分析未分配利润为负的历史原因。"}]</t>
+  </si>
+  <si>
+    <t>B2075</t>
+  </si>
+  <si>
+    <t>[{"Q":"贵州百灵2025年第三季度净利润同比增长100%，但营业总收入仅增长10%，请结合利润表和研报（如非经常性损益、产品结构优化），分析净利润高增长的原因。"}]</t>
+  </si>
+  <si>
+    <t>B2076</t>
+  </si>
+  <si>
+    <t>[{"Q":"2025年第三季度振东制药经营性现金流量净额同比下降超400%，请结合现金流量表和行业研报（如回款周期延长、付款政策收紧），分析现金流下降的原因。"}]</t>
+  </si>
+  <si>
+    <t>B2077</t>
+  </si>
+  <si>
+    <t>[{"Q":"结合近年中药材种植端的气候异常、病虫害及种植面积波动，以2-3家有自建种植基地的中药上市企业为例，分析其上游供应链自主可控策略（如订单农业、基地共建）对成本稳定性和产品质量的实际作用，并评估该策略的长期投入回报比。"}]</t>
+  </si>
+  <si>
+    <t>B2078</t>
+  </si>
+  <si>
+    <t>[{"Q":"中药上市企业的研发投入结构与新品上市周期存在怎样的关联？"}]</t>
+  </si>
+  <si>
+    <t>B2079</t>
+  </si>
+  <si>
+    <t>[{"Q":"政策支持下，中药企业的大健康产品布局如何影响营收结构？"}]</t>
+  </si>
+  <si>
+    <t>B2080</t>
+  </si>
+  <si>
+    <t>[{"Q":"中药材价格波动对不同规模中药企业的利润影响差异有多大？"},{"Q":"未来中药材价格波动趋势是什么，你判断的依据是什么"}]</t>
   </si>
 </sst>
 </file>
@@ -78,10 +552,23 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -551,142 +1038,142 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -695,6 +1182,21 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1222,9 +1724,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.61261261261261" defaultRowHeight="14.1" outlineLevelRow="3" outlineLevelCol="2"/>
+  <dimension ref="A1:C95"/>
+  <sheetFormatPr defaultColWidth="8.61261261261261" defaultRowHeight="14.1" outlineLevelCol="2"/>
   <cols>
+    <col min="1" max="1" width="8.61261261261261" style="1"/>
     <col min="2" max="2" width="16.7567567567568" customWidth="1"/>
     <col min="3" max="3" width="46.9459459459459" customWidth="1"/>
   </cols>
@@ -1240,7 +1743,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:3">
+    <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1251,7 +1754,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:3">
+    <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -1262,16 +1765,919 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:3">
+    <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>10</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>11</v>
       </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B22" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B23" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B24" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B25" t="s">
+        <v>39</v>
+      </c>
+      <c r="C25" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B26" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B27" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B28" t="s">
+        <v>39</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B29" t="s">
+        <v>39</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B30" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B31" t="s">
+        <v>39</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B32" t="s">
+        <v>39</v>
+      </c>
+      <c r="C32" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B33" t="s">
+        <v>39</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B34" t="s">
+        <v>39</v>
+      </c>
+      <c r="C34" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B35" t="s">
+        <v>39</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B36" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B37" t="s">
+        <v>80</v>
+      </c>
+      <c r="C37" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B38" t="s">
+        <v>80</v>
+      </c>
+      <c r="C38" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B39" t="s">
+        <v>80</v>
+      </c>
+      <c r="C39" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B40" t="s">
+        <v>80</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C41" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C42" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C43" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C44" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C45" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C46" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C47" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C48" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C49" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C50" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C51" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C53" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C54" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C55" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C56" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C57" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C58" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B61" t="s">
+        <v>10</v>
+      </c>
+      <c r="C61" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B62" t="s">
+        <v>10</v>
+      </c>
+      <c r="C62" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B63" t="s">
+        <v>10</v>
+      </c>
+      <c r="C63" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B64" t="s">
+        <v>10</v>
+      </c>
+      <c r="C64" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B65" t="s">
+        <v>10</v>
+      </c>
+      <c r="C65" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B66" t="s">
+        <v>10</v>
+      </c>
+      <c r="C66" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B67" t="s">
+        <v>10</v>
+      </c>
+      <c r="C67" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B68" t="s">
+        <v>10</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B69" t="s">
+        <v>10</v>
+      </c>
+      <c r="C69" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B70" t="s">
+        <v>10</v>
+      </c>
+      <c r="C70" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B71" t="s">
+        <v>10</v>
+      </c>
+      <c r="C71" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B72" t="s">
+        <v>10</v>
+      </c>
+      <c r="C72" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B73" t="s">
+        <v>10</v>
+      </c>
+      <c r="C73" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B74" t="s">
+        <v>10</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B75" t="s">
+        <v>10</v>
+      </c>
+      <c r="C75" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B76" t="s">
+        <v>10</v>
+      </c>
+      <c r="C76" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B77" t="s">
+        <v>10</v>
+      </c>
+      <c r="C77" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="B82" s="8"/>
+      <c r="C82" s="9"/>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="B83" s="8"/>
+      <c r="C83" s="9"/>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="B84" s="8"/>
+      <c r="C84" s="9"/>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="B85" s="8"/>
+      <c r="C85" s="9"/>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="B86" s="8"/>
+      <c r="C86" s="9"/>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="B87" s="8"/>
+      <c r="C87" s="9"/>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="B88" s="8"/>
+      <c r="C88" s="9"/>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="B89" s="8"/>
+      <c r="C89" s="9"/>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="B90" s="8"/>
+      <c r="C90" s="9"/>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="B91" s="8"/>
+      <c r="C91" s="9"/>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="B92" s="8"/>
+      <c r="C92" s="9"/>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="B93" s="8"/>
+      <c r="C93" s="9"/>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="B94" s="8"/>
+      <c r="C94" s="9"/>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="B95" s="8"/>
+      <c r="C95" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
